--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96554</v>
+        <v>96555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92209</v>
+        <v>92211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96555</v>
+        <v>96557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11103-2025 artfynd.xlsx
+++ b/artfynd/A 11103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132254445</v>
       </c>
       <c r="B2" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132254452</v>
       </c>
       <c r="B3" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>132254448</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
